--- a/server/resource/excel/template_product.xlsx
+++ b/server/resource/excel/template_product.xlsx
@@ -1,187 +1,111 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ted/Projects/gin-vue-admin/server/resource/excel/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1236F37C-450B-1C4A-9EF5-6D47E27110A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="11820" yWindow="500" windowWidth="24960" windowHeight="16300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="11820" yWindow="500" windowWidth="24960" windowHeight="16300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Product" sheetId="1" r:id="rId1"/>
+    <sheet name="Product" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
-  <si>
-    <r>
-      <t xml:space="preserve">        S&amp;L FOOD TRADING LTD
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color indexed="8"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">            10 Merbury Road  London  SE28 0HR</t>
-    </r>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>CODE</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRODUCT NAME</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>PACKING</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>EXP</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTY</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>PRICE</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>BARCODE</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>VAT</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-  <si>
-    <t>PHOTO</t>
-    <phoneticPr fontId="10" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="6">
-    <numFmt numFmtId="176" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ [$€-2]* #,##0.00_ ;_ [$€-2]* \-#,##0.00_ ;_ [$€-2]* &quot;-&quot;??_ "/>
-    <numFmt numFmtId="178" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
-    <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
-    <numFmt numFmtId="180" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="181" formatCode="[$£-809]#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="165" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="166" formatCode="[$£-809]#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="_([$€-2]* #,##0.00_);_([$€-2]* \(#,##0.00\);_([$€-2]* &quot;-&quot;??_)"/>
+    <numFmt numFmtId="168" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="169" formatCode="_ [$€-2]* #,##0.00_ ;_ [$€-2]* \-#,##0.00_ ;_ [$€-2]* &quot;-&quot;??_ "/>
   </numFmts>
   <fonts count="12">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="12"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
+    </font>
+    <font>
       <name val="Times New Roman"/>
       <family val="1"/>
-    </font>
-    <font>
       <sz val="12"/>
+    </font>
+    <font>
       <name val="宋体"/>
+      <charset val="134"/>
       <family val="3"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="12"/>
-      <color indexed="8"/>
+    </font>
+    <font>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
+      <color indexed="8"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="4"/>
       <sz val="9"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
+    </font>
+    <font>
       <name val="等线"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <b val="1"/>
+      <color theme="1"/>
       <sz val="9"/>
-      <color theme="1"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
+      <family val="2"/>
+      <sz val="9"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="4">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -194,7 +118,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0" tint="-4.9989318521683403E-2"/>
+        <fgColor theme="0" tint="-0.0499893185216834"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -209,109 +133,136 @@
     </border>
   </borders>
   <cellStyleXfs count="12">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="0">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="178" fontId="4" fillId="0" borderId="0">
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyProtection="1">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0"/>
+    <xf numFmtId="168" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="169" fontId="1" fillId="0" borderId="0" applyAlignment="1" applyProtection="1">
       <alignment vertical="top"/>
-      <protection locked="0"/>
+      <protection locked="0" hidden="0"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="31">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="180" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="181" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="179" fontId="9" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="12">
-    <cellStyle name="?鹎%U龡&amp;H鼼_x0008__x0001__x001f_?_x0007__x0001__x0001_" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="Normal 5" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="Normal 5 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="常规 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
-    <cellStyle name="常规 2 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
-    <cellStyle name="常规 4" xfId="9" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
-    <cellStyle name="常规 4 2" xfId="10" xr:uid="{00000000-0005-0000-0000-000008000000}"/>
-    <cellStyle name="千位分隔 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="千位分隔 2 2" xfId="6" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
-    <cellStyle name="样式 1" xfId="11" xr:uid="{00000000-0005-0000-0000-00000B000000}"/>
+    <cellStyle name="?鹎%U龡&amp;H鼼_x0008__x0001__x001f_?_x0007__x0001__x0001_" xfId="1"/>
+    <cellStyle name="Normal 2" xfId="2"/>
+    <cellStyle name="Normal 5" xfId="3"/>
+    <cellStyle name="Normal 5 2" xfId="4"/>
+    <cellStyle name="千位分隔 2" xfId="5"/>
+    <cellStyle name="千位分隔 2 2" xfId="6"/>
+    <cellStyle name="常规 2" xfId="7"/>
+    <cellStyle name="常规 2 2" xfId="8"/>
+    <cellStyle name="常规 4" xfId="9"/>
+    <cellStyle name="常规 4 2" xfId="10"/>
+    <cellStyle name="样式 1" xfId="11"/>
   </cellStyles>
   <dxfs count="4">
     <dxf>
@@ -356,316 +307,256 @@
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>923591</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>723900</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5537" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C0D790BC-1310-A51F-820D-AD76E34FCBBE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <to>
+      <col>0</col>
+      <colOff>923591</colOff>
+      <row>0</row>
+      <rowOff>723900</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5537" name="Picture 1"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId1"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      </blipFill>
+      <spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="57150"/>
           <a:ext cx="876300" cy="666750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>923591</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>723900</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5538" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F1CEA3B8-BE8C-4816-971E-02AA70613DE6}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <to>
+      <col>0</col>
+      <colOff>923591</colOff>
+      <row>0</row>
+      <rowOff>723900</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5538" name="Picture 2"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId2"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      </blipFill>
+      <spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="57150"/>
           <a:ext cx="876300" cy="666750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>923591</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>723900</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5539" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9D937431-EE64-ABA0-5FE7-2BE5C28CE60F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>0</row>
+      <rowOff>57150</rowOff>
+    </from>
+    <to>
+      <col>0</col>
+      <colOff>923591</colOff>
+      <row>0</row>
+      <rowOff>723900</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5539" name="Picture 3"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId3"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      </blipFill>
+      <spPr bwMode="auto">
         <a:xfrm>
           <a:off x="0" y="57150"/>
           <a:ext cx="876300" cy="666750"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>14288</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>909304</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>728663</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5540" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{80908A05-4462-E041-A4D5-587074C29513}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+  <twoCellAnchor editAs="oneCell">
+    <from>
+      <col>0</col>
+      <colOff>14288</colOff>
+      <row>0</row>
+      <rowOff>0</rowOff>
+    </from>
+    <to>
+      <col>0</col>
+      <colOff>909304</colOff>
+      <row>0</row>
+      <rowOff>728663</rowOff>
+    </to>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5540" name="Picture 4"/>
+        <cNvPicPr>
           <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
+        </cNvPicPr>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId4"/>
         <a:srcRect/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr bwMode="auto">
+      </blipFill>
+      <spPr bwMode="auto">
         <a:xfrm>
           <a:off x="14288" y="0"/>
           <a:ext cx="847725" cy="728663"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
-          <a:avLst/>
+          <avLst/>
         </a:prstGeom>
         <a:noFill/>
         <a:ln>
           <a:noFill/>
+          <a:prstDash val="solid"/>
         </a:ln>
-        <a:extLst>
-          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
-            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
-              <a:solidFill>
-                <a:srgbClr val="FFFFFF"/>
-              </a:solidFill>
-            </a14:hiddenFill>
-          </a:ext>
-          <a:ext uri="{91240B29-F687-4F45-9708-019B960494DF}">
-            <a14:hiddenLine xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" w="9525">
-              <a:solidFill>
-                <a:srgbClr val="000000"/>
-              </a:solidFill>
-              <a:miter lim="800000"/>
-              <a:headEnd/>
-              <a:tailEnd/>
-            </a14:hiddenLine>
-          </a:ext>
-        </a:extLst>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
+      </spPr>
+    </pic>
+    <clientData/>
+  </twoCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -964,114 +855,140 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J6"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="52.33203125" defaultRowHeight="75" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="16" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" style="15" customWidth="1"/>
-    <col min="3" max="3" width="19.6640625" style="17" customWidth="1"/>
-    <col min="4" max="4" width="7.83203125" style="18" customWidth="1"/>
-    <col min="5" max="5" width="10.1640625" style="19" customWidth="1"/>
-    <col min="6" max="6" width="8.5" style="7" customWidth="1"/>
-    <col min="7" max="7" width="8.33203125" style="8" customWidth="1"/>
-    <col min="8" max="8" width="14.5" style="16" customWidth="1"/>
-    <col min="9" max="9" width="7.5" style="16" customWidth="1"/>
-    <col min="10" max="16384" width="52.33203125" style="16"/>
+    <col width="13.6640625" customWidth="1" style="16" min="1" max="1"/>
+    <col width="7.33203125" customWidth="1" style="15" min="2" max="2"/>
+    <col width="19.6640625" customWidth="1" style="17" min="3" max="3"/>
+    <col width="7.83203125" customWidth="1" style="18" min="4" max="4"/>
+    <col width="10.1640625" customWidth="1" style="22" min="5" max="5"/>
+    <col width="8.5" customWidth="1" style="23" min="6" max="6"/>
+    <col width="8.33203125" customWidth="1" style="24" min="7" max="7"/>
+    <col width="14.5" customWidth="1" style="16" min="8" max="8"/>
+    <col width="14.5" customWidth="1" style="16" min="9" max="9"/>
+    <col width="7.5" customWidth="1" style="16" min="10" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="60" customHeight="1">
-      <c r="A1" s="15"/>
-      <c r="B1" s="21" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
+    <row r="1" ht="60" customHeight="1">
+      <c r="A1" s="15" t="n"/>
+      <c r="B1" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">        S&amp;L FOOD TRADING LTD
+            10 Merbury Road  London  SE28 0HR</t>
+        </is>
+      </c>
     </row>
-    <row r="2" spans="1:9" ht="9" customHeight="1"/>
-    <row r="3" spans="1:9" ht="37" customHeight="1">
-      <c r="A3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="G3" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>8</v>
+    <row r="2" ht="9" customHeight="1"/>
+    <row r="3" ht="37" customHeight="1">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>PHOTO</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>CODE</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>PRODUCT NAME</t>
+        </is>
+      </c>
+      <c r="D3" s="1" t="inlineStr">
+        <is>
+          <t>PACKING</t>
+        </is>
+      </c>
+      <c r="E3" s="25" t="inlineStr">
+        <is>
+          <t>EXP</t>
+        </is>
+      </c>
+      <c r="F3" s="25" t="inlineStr">
+        <is>
+          <t>QTY</t>
+        </is>
+      </c>
+      <c r="G3" s="26" t="inlineStr">
+        <is>
+          <t>PRICE</t>
+        </is>
+      </c>
+      <c r="H3" s="25" t="inlineStr">
+        <is>
+          <t>BARCODE</t>
+        </is>
+      </c>
+      <c r="I3" s="25" t="inlineStr">
+        <is>
+          <t>BARCODE(CASE)</t>
+        </is>
+      </c>
+      <c r="J3" s="25" t="inlineStr">
+        <is>
+          <t>VAT</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="75" customHeight="1">
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="6"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="8"/>
+    <row r="4" ht="75" customHeight="1">
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="H4" s="4" t="n"/>
+      <c r="J4" s="24" t="n"/>
     </row>
-    <row r="5" spans="1:9" ht="75" customHeight="1">
-      <c r="A5" s="20"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="10"/>
-      <c r="E5" s="11"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="13"/>
+    <row r="5" ht="75" customHeight="1">
+      <c r="A5" s="20" t="n"/>
+      <c r="B5" s="10" t="n"/>
+      <c r="C5" s="10" t="n"/>
+      <c r="D5" s="10" t="n"/>
+      <c r="E5" s="28" t="n"/>
+      <c r="F5" s="29" t="n"/>
+      <c r="G5" s="30" t="n"/>
+      <c r="H5" s="10" t="n"/>
+      <c r="J5" s="30" t="n"/>
     </row>
-    <row r="6" spans="1:9" ht="75" customHeight="1">
-      <c r="B6" s="4"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="6"/>
-      <c r="H6" s="9"/>
-      <c r="I6" s="8"/>
+    <row r="6" ht="75" customHeight="1">
+      <c r="B6" s="4" t="n"/>
+      <c r="D6" s="5" t="n"/>
+      <c r="E6" s="27" t="n"/>
+      <c r="H6" s="9" t="n"/>
+      <c r="J6" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:E1"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
   <conditionalFormatting sqref="A1 B2:B3 B6:B1048576">
-    <cfRule type="expression" dxfId="3" priority="33" stopIfTrue="1">
+    <cfRule type="expression" priority="33" dxfId="0" stopIfTrue="1">
       <formula>AND(COUNTIF($A$1:$A$1, A1)+COUNTIF($B$2:$B$65534, A1)&gt;1,NOT(ISBLANK(A1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A3">
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
+    <cfRule type="expression" priority="3" dxfId="0" stopIfTrue="1">
       <formula>AND(COUNTIF($A$1:$A$1, A3)+COUNTIF($B$2:$B$65534, A3)&gt;1,NOT(ISBLANK(A3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B4:B5">
-    <cfRule type="expression" dxfId="1" priority="1" stopIfTrue="1">
+    <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>AND(COUNTIF($A$1:$A$1, B4)+COUNTIF($A$2:$A$65534, B4)&gt;1,NOT(ISBLANK(B4)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C3">
-    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
+    <cfRule type="expression" priority="4" dxfId="0" stopIfTrue="1">
       <formula>AND(COUNTIF($A$1:$A$1, C3)+COUNTIF($B$2:$B$65534, C3)&gt;1,NOT(ISBLANK(C3)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0" right="0" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>